--- a/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92994994498</v>
+        <v>46157.93083828073</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93083828073</v>
+        <v>46157.93353111069</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93353111069</v>
+        <v>46157.93642627195</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93642627195</v>
+        <v>46158.28178392004</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итоги по группам" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость файлов'!$A$8:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость файлов'!$A$8:$G$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28178392004</v>
+        <v>46158.29754595234</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46157.92969689964</v>
+        <v>46158.29722418641</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       <c r="H9" s="1" t="n"/>
       <c r="I9" s="1" t="n"/>
     </row>
-    <row r="10" ht="105" customHeight="1">
+    <row r="10" ht="120" customHeight="1">
       <c r="A10" s="9" t="n">
         <v>2</v>
       </c>
@@ -750,7 +750,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>09.1_442-FZ_кандидат.pdf</t>
+          <t>09.1_442-FZ_от_28.12.2013.pdf</t>
         </is>
       </c>
       <c r="D10" s="12" t="n">
@@ -764,13 +764,13 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.1_442-FZ_кандидат.pdf</t>
+          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.1_442-FZ_от_28.12.2013.pdf</t>
         </is>
       </c>
       <c r="H10" s="1" t="n"/>
       <c r="I10" s="1" t="n"/>
     </row>
-    <row r="11" ht="105" customHeight="1">
+    <row r="11" ht="135" customHeight="1">
       <c r="A11" s="9" t="n">
         <v>3</v>
       </c>
@@ -781,7 +781,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>09.2_557-P_кандидат.pdf</t>
+          <t>09.2_Постановление_557-П_от_25.06.2021.pdf</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.2_557-P_кандидат.pdf</t>
+          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.2_Постановление_557-П_от_25.06.2021.pdf</t>
         </is>
       </c>
       <c r="H11" s="1" t="n"/>
@@ -843,29 +843,27 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>09.5_Постановление_РФ_№1236_от_24.11.2014.docx</t>
+          <t>09.5_Постановление_РФ_№1236_от_24.11.2014.pdf</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>12.3</v>
+        <v>141.9</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>46157.58168981481</v>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>46157.58170138889</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>3</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.5_Постановление_РФ_№1236_от_24.11.2014.docx</t>
+          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.5_Постановление_РФ_№1236_от_24.11.2014.pdf</t>
         </is>
       </c>
       <c r="H13" s="1" t="n"/>
       <c r="I13" s="1" t="n"/>
     </row>
-    <row r="14" ht="135" customHeight="1">
+    <row r="14" ht="150" customHeight="1">
       <c r="A14" s="9" t="n">
         <v>6</v>
       </c>
@@ -876,27 +874,27 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>09.5_Постановление_РФ_№1236_от_24.11.2014.pdf</t>
+          <t>09.6_Постановление Правительства РФ от 01.12.2014 № 1285.pdf</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>141.9</v>
+        <v>604.7</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>46157.58170138889</v>
+        <v>46140.72214230907</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.5_Постановление_РФ_№1236_от_24.11.2014.pdf</t>
+          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.6_Постановление Правительства РФ от 01.12.2014 № 1285.pdf</t>
         </is>
       </c>
       <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
     </row>
-    <row r="15" ht="150" customHeight="1">
+    <row r="15" ht="165" customHeight="1">
       <c r="A15" s="9" t="n">
         <v>7</v>
       </c>
@@ -907,27 +905,27 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>09.6_Постановление Правительства РФ от 01.12.2014 № 1285.pdf</t>
+          <t>09.7_Постановление Правительства ЯНАО от 25.12.2015 № 1306-П.pdf</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>604.7</v>
+        <v>275.8</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>46140.72214230907</v>
+        <v>46140.72978671999</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.6_Постановление Правительства РФ от 01.12.2014 № 1285.pdf</t>
+          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.7_Постановление Правительства ЯНАО от 25.12.2015 № 1306-П.pdf</t>
         </is>
       </c>
       <c r="H15" s="1" t="n"/>
       <c r="I15" s="1" t="n"/>
     </row>
-    <row r="16" ht="165" customHeight="1">
+    <row r="16" ht="150" customHeight="1">
       <c r="A16" s="9" t="n">
         <v>8</v>
       </c>
@@ -938,27 +936,27 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>09.7_Постановление Правительства ЯНАО от 25.12.2015 № 1306-П.pdf</t>
+          <t>09.8_Постановление Правительства ЯНАО от 13.03.2026 № 129-П.pdf</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>275.8</v>
+        <v>191</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>46140.72978671999</v>
+        <v>46140.77170517622</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>10</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.7_Постановление Правительства ЯНАО от 25.12.2015 № 1306-П.pdf</t>
+          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.8_Постановление Правительства ЯНАО от 13.03.2026 № 129-П.pdf</t>
         </is>
       </c>
       <c r="H16" s="1" t="n"/>
       <c r="I16" s="1" t="n"/>
     </row>
-    <row r="17" ht="150" customHeight="1">
+    <row r="17" ht="165" customHeight="1">
       <c r="A17" s="9" t="n">
         <v>9</v>
       </c>
@@ -969,59 +967,28 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>09.8_Постановление Правительства ЯНАО от 13.03.2026 № 129-П.pdf</t>
+          <t>09.9_Диаграмма динамики инфляции ЯНАО и России 2019–2025 гг..pdf</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>191</v>
+        <v>402.9</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>46140.77170517622</v>
+        <v>46140.68394272676</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.8_Постановление Правительства ЯНАО от 13.03.2026 № 129-П.pdf</t>
+          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.9_Диаграмма динамики инфляции ЯНАО и России 2019–2025 гг..pdf</t>
         </is>
       </c>
       <c r="H17" s="1" t="n"/>
       <c r="I17" s="1" t="n"/>
     </row>
-    <row r="18" ht="165" customHeight="1">
-      <c r="A18" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>09_Нормативка</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>09.9_Диаграмма динамики инфляции ЯНАО и России 2019–2025 гг..pdf</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>402.9</v>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>46140.68394272676</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>C:\taganay_svod_2024\Дело3а-78-2026Таганай\09_Нормативка\09.9_Диаграмма динамики инфляции ЯНАО и России 2019–2025 гг..pdf</t>
-        </is>
-      </c>
-      <c r="H18" s="1" t="n"/>
-      <c r="I18" s="1" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A8:G18"/>
+  <autoFilter ref="A8:G17"/>
   <mergeCells count="3">
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B2:G2"/>
@@ -1119,19 +1086,19 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>109</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46032.65003856993</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>46157.92969689964</v>
+        <v>46158.29722418641</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29754595234</v>
+        <v>46158.29773111471</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29773111471</v>
+        <v>46158.30446689167</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.30446689167</v>
+        <v>46158.3334172592</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3334172592</v>
+        <v>46158.37202261235</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37202261235</v>
+        <v>46158.37418865754</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -724,7 +724,7 @@
         <v>7.1</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46158.29722418641</v>
+        <v>46158.37379392594</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46032.65003856993</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>46158.29722418641</v>
+        <v>46158.37379392594</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
